--- a/vse-loti/339447955/spec-339447955.xlsx
+++ b/vse-loti/339447955/spec-339447955.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -58,12 +60,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,14 +437,14 @@
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -502,14 +505,24 @@
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="3" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>НМЦК из обоснования:</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>1561883</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Источник: 852615596.htm</t>
+          <t>Источник: 852615596.txt</t>
         </is>
       </c>
     </row>

--- a/vse-loti/339447955/spec-339447955.xlsx
+++ b/vse-loti/339447955/spec-339447955.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -60,13 +61,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -500,27 +503,129 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Затвор поворотно-дисковый</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" s="3" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>18000</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0</v>
+        <v>195000</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>15000</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>НМЦК из обоснования:</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Затвор поворотно-дисковый</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" s="3" t="n">
+        <v>105050</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>126060</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>1561883</v>
+        <v>1365650</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>105050</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>126060</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Клапан для труб</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Штука</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" s="3" t="n">
+        <v>308.33</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>370</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>1233.32</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>308.33</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>370</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1561883.32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>НМЦК из обоснования:</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>1561883</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Источник: 852615596.txt</t>
         </is>

--- a/vse-loti/339447955/spec-339447955.xlsx
+++ b/vse-loti/339447955/spec-339447955.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -66,10 +65,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -446,8 +445,6 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,25 +475,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (без НДС)</t>
+          <t>Стоимость (без НДС)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (с НДС)</t>
+          <t>Цена за т (без НДС)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Стоимость (без НДС)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
@@ -521,20 +508,10 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" s="3" t="n">
-        <v>15000</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>18000</v>
-      </c>
-      <c r="H2" s="3" t="n">
         <v>195000</v>
       </c>
-      <c r="I2" s="3" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>18000</v>
-      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -555,20 +532,10 @@
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" s="3" t="n">
-        <v>105050</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>126060</v>
-      </c>
-      <c r="H3" s="3" t="n">
         <v>1365650</v>
       </c>
-      <c r="I3" s="3" t="n">
-        <v>105050</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>126060</v>
-      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -589,20 +556,10 @@
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" s="3" t="n">
-        <v>308.33</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>370</v>
-      </c>
-      <c r="H4" s="3" t="n">
         <v>1233.32</v>
       </c>
-      <c r="I4" s="3" t="n">
-        <v>308.33</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>370</v>
-      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -610,7 +567,7 @@
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="F5" s="5" t="n">
         <v>1561883.32</v>
       </c>
     </row>
@@ -620,7 +577,7 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="F6" s="5" t="n">
         <v>1561883</v>
       </c>
     </row>

--- a/vse-loti/339447955/spec-339447955.xlsx
+++ b/vse-loti/339447955/spec-339447955.xlsx
@@ -17,9 +17,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,14 +28,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FF808080"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,7 +52,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00305496"/>
+        <fgColor rgb="FF305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -60,15 +73,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,17 +462,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,35 +484,40 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Наименование позиции (⌀ + s, если указано)</t>
+          <t>Наименование позиции</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Характеристика (D×s / DN, PN, материал)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Кол-во (исх.)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Масса, т (приведённая)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Цена за т (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
@@ -495,23 +529,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Затвор поворотно-дисковый</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
+          <t>Затвор поворотно-дисковый межфланцевый с электроприводом, DN ≥ 150, PN 16, корпус — серый чугун, диск — нерж. сталь CF8M, класс герметичности А, IP 67</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>DN ≥ 150 мм; PN 16; D×s: см. ТЗ; серый чугун / CF8M</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" s="3" t="n">
-        <v>195000</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>162500</v>
+      </c>
+      <c r="H2" s="5" t="inlineStr"/>
+      <c r="I2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -519,23 +557,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Затвор поворотно-дисковый</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
+          <t>Затвор поворотно-дисковый межфланцевый с электроприводом, DN ≥ 200, PN 16, корпус — серый чугун, диск — нерж. сталь CF8M, класс герметичности А, IP 67</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>DN ≥ 200 мм; PN 16; D×s: см. ТЗ; серый чугун / CF8M</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" s="3" t="n">
-        <v>1365650</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>1138041.67</v>
+      </c>
+      <c r="H3" s="5" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -543,48 +585,78 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Клапан для труб</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
+          <t>Клапан для труб обратный муфтовый, DN ≥ 15, PN ≥ 4 МПа, корпус — латунь, соединение муфтовое, рабочая среда — горячая вода</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>DN ≥ 15 мм; PN ≥ 4 МПа; латунь; муфтовый</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Штука</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" s="3" t="n">
-        <v>1233.32</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>1027.77</v>
+      </c>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="9" t="n">
+        <v>1301569.43</v>
+      </c>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>НМЦК (без НДС):</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>1301569.43</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>НМЦК (с НДС):</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="n">
         <v>1561883.32</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>НМЦК из обоснования:</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>1561883</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Источник: 852615596.txt</t>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Источник 1 (позиции, кол-во, цены, хар-ки): Извещение 0373500003226000061 (852615596.htm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Источник 2 (подтверждение НМЦК): Расчет НМЦК(Д) — xlsx (852615594.zip → _nmck_unzipped/)</t>
         </is>
       </c>
     </row>
